--- a/app/src/main/assets/Pipistrelli 2023.xlsx
+++ b/app/src/main/assets/Pipistrelli 2023.xlsx
@@ -573,7 +573,11 @@
           <t>Villaverla</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>45.6499676</v>
       </c>
@@ -625,7 +629,11 @@
           <t>Montebello vicentino</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>45.4596014</v>
       </c>
@@ -677,7 +685,11 @@
           <t>Monte di Malo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>45.6619177</v>
       </c>
@@ -785,7 +797,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.45985</v>
       </c>
@@ -893,7 +909,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>45.661886</v>
       </c>
@@ -1001,7 +1021,11 @@
           <t>Zovencedo</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>45.4300235</v>
       </c>
@@ -1221,7 +1245,11 @@
           <t>Valli del Pasubio</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>45.7398938</v>
       </c>
@@ -1273,7 +1301,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>45.6403</v>
       </c>
@@ -1325,7 +1357,11 @@
           <t>Schiavon</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>45.6777651</v>
       </c>
@@ -1545,7 +1581,11 @@
           <t>Isola Vicentina</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>45.6299029</v>
       </c>
@@ -1599,7 +1639,11 @@
           <t>Fara Vicentino</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>45.7395927</v>
       </c>
@@ -1747,7 +1791,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>45.6285174</v>
       </c>
@@ -1903,7 +1951,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>45.4318813</v>
       </c>
@@ -2067,7 +2119,11 @@
           <t>Chiampo</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>45.5445732</v>
       </c>
@@ -2115,7 +2171,11 @@
           <t>Valbrenta</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>45.8241443</v>
       </c>
@@ -2163,7 +2223,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>45.4709699</v>
       </c>
@@ -2215,7 +2279,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>45.5004723</v>
       </c>
@@ -2431,7 +2499,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>45.4517637</v>
       </c>
@@ -2535,7 +2607,11 @@
           <t>Grumolo delle Abbadesse</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>45.5163094</v>
       </c>
@@ -2583,7 +2659,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>45.48688</v>
       </c>
@@ -2635,7 +2715,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>45.4081213</v>
       </c>
@@ -2687,7 +2771,11 @@
           <t>Monticello Conte Otto</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>45.5925277</v>
       </c>
@@ -2963,7 +3051,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>45.7201187</v>
       </c>
@@ -3017,7 +3109,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>45.7056839</v>
       </c>
@@ -3177,7 +3273,11 @@
           <t>Sarego</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>45.4081213</v>
       </c>
@@ -3285,7 +3385,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>45.7201187</v>
       </c>
@@ -3447,7 +3551,11 @@
           <t>Camisano Vicentino</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>45.5220266</v>
       </c>
@@ -3719,7 +3827,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>45.6355174</v>
       </c>
@@ -3827,7 +3939,11 @@
           <t>Montebello Vicentino</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>45.4572159</v>
       </c>
@@ -3879,7 +3995,11 @@
           <t>Campiglia dei Berici</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>45.3362423</v>
       </c>
@@ -4325,7 +4445,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>45.7034884</v>
       </c>
@@ -4377,7 +4501,11 @@
           <t>Calvene</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>45.7659086</v>
       </c>
@@ -4485,7 +4613,11 @@
           <t>Montegaldella</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>45.430864</v>
       </c>
@@ -4537,7 +4669,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>45.6641897</v>
       </c>
@@ -4701,7 +4837,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>45.6585696</v>
       </c>
@@ -4913,7 +5053,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>45.5004723</v>
       </c>
@@ -5017,7 +5161,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>45.4721218</v>
       </c>
@@ -5065,11 +5213,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>45.4083415</v>
       </c>
@@ -5121,11 +5265,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>45.4083415</v>
       </c>
@@ -5177,7 +5317,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>45.4437746</v>
       </c>
@@ -5225,7 +5369,11 @@
           <t>Cogollo del Cengio</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>45.7852211</v>
       </c>
@@ -5277,11 +5425,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>45.4083415</v>
       </c>
@@ -5385,7 +5529,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>45.7244163</v>
       </c>
@@ -5489,7 +5637,11 @@
           <t>Alonte</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>45.3650367</v>
       </c>
@@ -5541,7 +5693,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>45.4612318</v>
       </c>
@@ -5705,7 +5861,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>45.5004723</v>
       </c>
@@ -5757,7 +5917,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>45.4930641</v>
       </c>
@@ -5865,7 +6029,11 @@
           <t>Asiago</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>45.8753771</v>
       </c>
@@ -5973,7 +6141,11 @@
           <t>Piazzola sul Brenta</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>45.5797865</v>
       </c>
@@ -6025,7 +6197,11 @@
           <t>Tezze sul Brenta</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>45.6861778</v>
       </c>
@@ -6301,7 +6477,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>45.5004723</v>
       </c>

--- a/app/src/main/assets/Pipistrelli 2023.xlsx
+++ b/app/src/main/assets/Pipistrelli 2023.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di Malo</t>
+          <t>Monte di malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del Pasubio</t>
+          <t>Valli del pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola Vicentina</t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara Vicentino</t>
+          <t>Fara vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla Vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano Vicentino</t>
+          <t>Bolzano vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle Abbadesse</t>
+          <t>Grumolo delle abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio Maggiore</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3642,14 +3642,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Due Ville</t>
+          <t>Dueville</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>VI</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>45.8144577</v>
+        <v>45.5479</v>
       </c>
       <c r="I61" t="n">
-        <v>15.9798551</v>
+        <v>11.5446</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3802,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello Vicentino</t>
+          <t>Montebello vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3856,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei Berici</t>
+          <t>Campiglia dei berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3910,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto Vicentino</t>
+          <t>Quinto vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4723,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4826,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5174,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del Cengio</t>
+          <t>Cogollo del cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5915,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul Brenta</t>
+          <t>Piazzola sul brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul Brenta</t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/app/src/main/assets/Pipistrelli 2023.xlsx
+++ b/app/src/main/assets/Pipistrelli 2023.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monte di malo</t>
+          <t>Monte Di Malo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Valli del pasubio</t>
+          <t>Valli Del Pasubio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fara vicentino</t>
+          <t>Fara Vicentino</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolzano vicentino</t>
+          <t>Bolzano Vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grumolo delle abbadesse</t>
+          <t>Grumolo Delle Abbadesse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montebello vicentino</t>
+          <t>Montebello Vicentino</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Campiglia dei berici</t>
+          <t>Campiglia Dei Berici</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quinto vicentino</t>
+          <t>Quinto Vicentino</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo del cengio</t>
+          <t>Cogollo Del Cengio</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola sul brenta</t>
+          <t>Piazzola Sul Brenta</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">

--- a/app/src/main/assets/Pipistrelli 2023.xlsx
+++ b/app/src/main/assets/Pipistrelli 2023.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,6 +506,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Piazza del Castello</t>
@@ -545,9 +546,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44950</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,6 +562,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Via San Leonardo Murialdo 21</t>
@@ -576,10 +579,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>45.6499676</v>
+        <v>45.60331</v>
       </c>
       <c r="I3" t="n">
-        <v>11.4986907</v>
+        <v>11.49392</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -599,9 +602,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -614,6 +618,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Via San Francesco</t>
@@ -653,9 +658,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44998</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -668,6 +674,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Via San Rocco 27</t>
@@ -684,10 +691,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45.6619177</v>
+        <v>45.66547</v>
       </c>
       <c r="I5" t="n">
-        <v>11.3639604</v>
+        <v>11.37038</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -707,9 +714,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>45003</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -722,6 +730,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Via Risorgimento 46</t>
@@ -738,10 +747,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.4970909</v>
+        <v>45.48512</v>
       </c>
       <c r="I6" t="n">
-        <v>11.4894451</v>
+        <v>11.48805</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -761,9 +770,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>45003</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -776,6 +786,7 @@
           <t>Rhinolophus ferrumequinum</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Lumignano</t>
@@ -815,9 +826,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>45012</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,6 +842,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Ferrovieri</t>
@@ -869,9 +882,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>45014</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,6 +898,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Via Aldo Moro</t>
@@ -923,9 +938,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>45045</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -938,6 +954,7 @@
           <t>Plecotus auritus</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Via Regina Margherita</t>
@@ -977,9 +994,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>45057</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -992,6 +1010,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Via Roma</t>
@@ -1031,9 +1050,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1046,6 +1066,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1085,9 +1106,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1100,6 +1122,7 @@
           <t>Nyctalus leisleri</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Via Fioretta 8</t>
@@ -1116,10 +1139,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>45.645818</v>
+        <v>45.64205</v>
       </c>
       <c r="I13" t="n">
-        <v>11.2928279</v>
+        <v>11.30653</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1139,9 +1162,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1154,6 +1178,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Via delle Fornaci 72</t>
@@ -1170,10 +1195,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>45.6348591</v>
+        <v>45.53934</v>
       </c>
       <c r="I14" t="n">
-        <v>11.4063543</v>
+        <v>11.52309</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1193,9 +1218,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45080</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1208,6 +1234,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Via Guglielmo Marconi</t>
@@ -1247,9 +1274,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45084</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1262,6 +1290,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Via Corvo 62</t>
@@ -1278,10 +1307,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>45.6403</v>
+        <v>45.63228</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5512138</v>
+        <v>11.55417</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1301,9 +1330,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45096</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1316,6 +1346,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Via Sila 3</t>
@@ -1332,10 +1363,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.6777651</v>
+        <v>45.70132</v>
       </c>
       <c r="I17" t="n">
-        <v>11.6434259</v>
+        <v>11.64415</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1355,9 +1386,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1370,6 +1402,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Via Sacchi Bortolo, 32</t>
@@ -1386,10 +1419,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.7502752</v>
+        <v>45.75391</v>
       </c>
       <c r="I18" t="n">
-        <v>11.7221597</v>
+        <v>11.72844</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1409,9 +1442,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1424,6 +1458,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Via Sacchi Bortolo, 32</t>
@@ -1440,10 +1475,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45.7502752</v>
+        <v>45.75391</v>
       </c>
       <c r="I19" t="n">
-        <v>11.7221597</v>
+        <v>11.72844</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1463,9 +1498,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45102</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1478,6 +1514,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1517,9 +1554,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45102</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1532,6 +1570,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Via Monte Novegno</t>
@@ -1576,7 +1615,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1589,6 +1628,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Fara Vicentino</t>
@@ -1618,14 +1658,16 @@
       <c r="K22" t="n">
         <v>1</v>
       </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1638,6 +1680,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>via Tavernelle 9</t>
@@ -1654,10 +1697,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>45.5140939</v>
+        <v>45.5154</v>
       </c>
       <c r="I23" t="n">
-        <v>11.4574964</v>
+        <v>11.46247</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1667,14 +1710,16 @@
       <c r="K23" t="n">
         <v>1</v>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1687,6 +1732,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>San Giorgio di Perlena</t>
@@ -1697,6 +1743,7 @@
           <t>San Giorgio di Perlena</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>45.7304755</v>
       </c>
@@ -1711,14 +1758,16 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1731,6 +1780,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>via Revoloni 24</t>
@@ -1747,10 +1797,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45.6285174</v>
+        <v>45.63551</v>
       </c>
       <c r="I25" t="n">
-        <v>11.5476187</v>
+        <v>11.54884</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1770,9 +1820,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1785,6 +1836,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>via Lago di Vico 60</t>
@@ -1801,10 +1853,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>45.7199703</v>
+        <v>45.71346</v>
       </c>
       <c r="I26" t="n">
-        <v>11.4133487</v>
+        <v>11.35844</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1814,14 +1866,16 @@
       <c r="K26" t="n">
         <v>1</v>
       </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1834,6 +1888,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>via Da Vinci 32</t>
@@ -1850,10 +1905,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>45.53057</v>
+        <v>45.5342</v>
       </c>
       <c r="I27" t="n">
-        <v>11.4778668</v>
+        <v>11.4845</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1863,14 +1918,16 @@
       <c r="K27" t="n">
         <v>1</v>
       </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1883,6 +1940,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>via Silvio Pellico</t>
@@ -1922,9 +1980,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1937,6 +1996,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>via Vespucci 11</t>
@@ -1953,10 +2013,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>45.5560012</v>
+        <v>45.55633</v>
       </c>
       <c r="I29" t="n">
-        <v>11.519238</v>
+        <v>11.51875</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1976,9 +2036,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>45105</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1991,6 +2052,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Via Don Zilotto</t>
@@ -2030,9 +2092,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>45105</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2045,6 +2108,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Chiampo</t>
@@ -2074,14 +2138,16 @@
       <c r="K31" t="n">
         <v>1</v>
       </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>45105</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2094,6 +2160,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Via Monte Ortigara</t>
@@ -2123,14 +2190,16 @@
       <c r="K32" t="n">
         <v>1</v>
       </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>45106</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2143,6 +2212,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2182,9 +2252,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>45106</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2197,6 +2268,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -2236,9 +2308,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>45106</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2251,6 +2324,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Ospedale Civile di Vicenza San Bortolo</t>
@@ -2290,9 +2364,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>45106</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2305,6 +2380,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Bolzano Vicentino</t>
@@ -2334,14 +2410,16 @@
       <c r="K36" t="n">
         <v>1</v>
       </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2354,6 +2432,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile 18/5</t>
@@ -2370,10 +2449,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>45.7059893</v>
+        <v>45.70679</v>
       </c>
       <c r="I37" t="n">
-        <v>11.4797197</v>
+        <v>11.47426</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2393,9 +2472,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2408,6 +2488,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Via Mazzini 27</t>
@@ -2424,10 +2505,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>45.4517637</v>
+        <v>45.4542</v>
       </c>
       <c r="I38" t="n">
-        <v>11.3824998</v>
+        <v>11.3831</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2447,9 +2528,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2462,6 +2544,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2491,14 +2574,16 @@
       <c r="K39" t="n">
         <v>1</v>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>45109</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2511,6 +2596,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Grumolo delle Abbadesse</t>
@@ -2540,14 +2626,16 @@
       <c r="K40" t="n">
         <v>1</v>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>45109</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2560,6 +2648,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Spianzana</t>
@@ -2599,9 +2688,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>45110</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2614,6 +2704,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Sarego</t>
@@ -2653,9 +2744,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>45110</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2668,6 +2760,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>via Europa 119</t>
@@ -2684,10 +2777,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>45.5925277</v>
+        <v>45.59552</v>
       </c>
       <c r="I43" t="n">
-        <v>11.5686495</v>
+        <v>11.58217</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2707,9 +2800,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>45111</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2722,6 +2816,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2766,7 +2861,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>45111</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2779,6 +2874,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>via Molini 50a</t>
@@ -2795,10 +2891,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>45.529767</v>
+        <v>45.5312</v>
       </c>
       <c r="I45" t="n">
-        <v>11.455545</v>
+        <v>11.4883</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2818,9 +2914,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2833,6 +2930,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Via Mon Signor Pertile 18/5</t>
@@ -2849,10 +2947,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45.7059893</v>
+        <v>45.70679</v>
       </c>
       <c r="I46" t="n">
-        <v>11.4797197</v>
+        <v>11.47426</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2872,9 +2970,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2887,6 +2986,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -2926,12 +3026,13 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>45113</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="1" t="n">
         <v>22.525</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2939,6 +3040,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -2983,7 +3085,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2996,6 +3098,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Via Giacomo Zanella 71 A</t>
@@ -3012,10 +3115,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>45.7056839</v>
+        <v>45.7081</v>
       </c>
       <c r="I49" t="n">
-        <v>11.5678638</v>
+        <v>11.5644</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3035,9 +3138,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3050,6 +3154,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3079,14 +3184,16 @@
       <c r="K50" t="n">
         <v>1</v>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3099,6 +3206,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Strada delle Cattane 71</t>
@@ -3115,10 +3223,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>45.5462004</v>
+        <v>45.5401</v>
       </c>
       <c r="I51" t="n">
-        <v>11.5104295</v>
+        <v>11.5167</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3138,9 +3246,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>45115</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3153,6 +3262,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Sarego</t>
@@ -3192,9 +3302,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>45115</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3207,6 +3318,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve"> contrà motton pusterla 2</t>
@@ -3223,10 +3335,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45.5501072</v>
+        <v>45.55024</v>
       </c>
       <c r="I53" t="n">
-        <v>11.5457041</v>
+        <v>11.54345</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3246,9 +3358,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>45115</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3261,6 +3374,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -3305,7 +3419,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>45116</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3318,6 +3432,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Contra Porta Padova, 46</t>
@@ -3334,10 +3449,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>45.5496207</v>
+        <v>45.54928</v>
       </c>
       <c r="I55" t="n">
-        <v>11.5536058</v>
+        <v>11.55404</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3347,14 +3462,16 @@
       <c r="K55" t="n">
         <v>1</v>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>45116</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3367,6 +3484,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Via Abruzzo 2</t>
@@ -3383,10 +3501,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>45.5050793</v>
+        <v>45.49845</v>
       </c>
       <c r="I56" t="n">
-        <v>11.4084448</v>
+        <v>11.41725</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3406,9 +3524,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>45116</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3421,6 +3540,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Camisano Vicentino</t>
@@ -3450,14 +3570,16 @@
       <c r="K57" t="n">
         <v>1</v>
       </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3470,6 +3592,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>via Monsignor Pertile 19/23</t>
@@ -3486,10 +3609,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>45.6348591</v>
+        <v>45.53982</v>
       </c>
       <c r="I58" t="n">
-        <v>11.4063543</v>
+        <v>11.53112</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3509,9 +3632,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3524,6 +3648,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Santa Bertilla</t>
@@ -3568,7 +3693,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3581,6 +3706,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Contrà della Misericordia 24</t>
@@ -3597,10 +3723,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>45.5526214</v>
+        <v>45.55225</v>
       </c>
       <c r="I60" t="n">
-        <v>11.5426385</v>
+        <v>11.54316</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3620,9 +3746,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3635,6 +3762,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Via Industria 57</t>
@@ -3651,10 +3779,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>45.5479</v>
+        <v>45.62635</v>
       </c>
       <c r="I61" t="n">
-        <v>11.5446</v>
+        <v>11.54228</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3679,7 +3807,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3692,6 +3820,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>via Sabbionara 1</t>
@@ -3708,10 +3837,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>45.6355174</v>
+        <v>45.6329</v>
       </c>
       <c r="I62" t="n">
-        <v>11.5485978</v>
+        <v>11.54884</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3731,9 +3860,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3746,6 +3876,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -3785,9 +3916,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3800,6 +3932,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Montebello Vicentino</t>
@@ -3839,9 +3972,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3854,6 +3988,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>via Armedola 4 Lanze'</t>
@@ -3870,10 +4005,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>45.3362423</v>
+        <v>45.34415</v>
       </c>
       <c r="I65" t="n">
-        <v>11.5394891</v>
+        <v>11.53912</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3893,9 +4028,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>45120</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3908,6 +4044,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Quinto Vicentino</t>
@@ -3947,9 +4084,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3962,6 +4100,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Via Botticelli 6</t>
@@ -3978,10 +4117,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>45.7116058</v>
+        <v>45.53238</v>
       </c>
       <c r="I67" t="n">
-        <v>11.4928835</v>
+        <v>11.51655</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4001,9 +4140,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4016,6 +4156,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Strada Ca' Balbi</t>
@@ -4055,9 +4196,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>45122</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4070,6 +4212,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Via Villa Beltrame 6</t>
@@ -4086,10 +4229,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45.6987902</v>
+        <v>45.71968</v>
       </c>
       <c r="I69" t="n">
-        <v>11.3981595</v>
+        <v>11.36384</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4109,9 +4252,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>45122</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4124,6 +4268,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Osteria Veneto's, 56, Corso Andrea Palladio</t>
@@ -4140,10 +4285,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>45.5470273</v>
+        <v>45.54751</v>
       </c>
       <c r="I70" t="n">
-        <v>11.5434297</v>
+        <v>11.54583</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4168,7 +4313,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>45123</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4181,6 +4326,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4220,9 +4366,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>45123</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4235,6 +4382,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>strada del Molino 10</t>
@@ -4251,10 +4399,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>45.6988924</v>
+        <v>45.54582</v>
       </c>
       <c r="I72" t="n">
-        <v>11.5573731</v>
+        <v>11.51654</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4274,9 +4422,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>45125</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4289,6 +4438,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Via Giacomo Zanella</t>
@@ -4328,9 +4478,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>45125</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4343,6 +4494,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Viale Margherita vicino allo stadio</t>
@@ -4382,9 +4534,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>45126</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4397,6 +4550,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Via Marco Polo</t>
@@ -4436,9 +4590,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>45126</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4451,6 +4606,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Stradone Fedele Lampertico</t>
@@ -4490,9 +4646,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>45127</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4505,6 +4662,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Via Silvio Pellico</t>
@@ -4544,9 +4702,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>45127</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4559,6 +4718,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -4598,9 +4758,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4613,6 +4774,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Via Tintoretto 5</t>
@@ -4629,10 +4791,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>45.7113511</v>
+        <v>45.71714</v>
       </c>
       <c r="I79" t="n">
-        <v>11.3553593</v>
+        <v>11.36531</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4652,9 +4814,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>45129</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4667,6 +4830,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Largo Europa 1</t>
@@ -4683,10 +4847,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>45.6585696</v>
+        <v>45.66014</v>
       </c>
       <c r="I80" t="n">
-        <v>11.405103</v>
+        <v>11.41721</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4706,9 +4870,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>45131</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4721,6 +4886,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Viale Francesco Crispi 142</t>
@@ -4737,10 +4903,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>45.7051709</v>
+        <v>45.71215</v>
       </c>
       <c r="I81" t="n">
-        <v>11.2249347</v>
+        <v>11.23412</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4760,9 +4926,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>45132</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4775,6 +4942,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4804,14 +4972,16 @@
       <c r="K82" t="n">
         <v>1</v>
       </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4824,6 +4994,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -4853,14 +5024,16 @@
       <c r="K83" t="n">
         <v>1</v>
       </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4873,6 +5046,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -4912,9 +5086,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4927,6 +5102,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Strada della pilla 25A</t>
@@ -4937,11 +5113,12 @@
           <t>Zané</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>45.7201187</v>
+        <v>45.72314</v>
       </c>
       <c r="I85" t="n">
-        <v>11.4608274</v>
+        <v>11.44853</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4961,9 +5138,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4976,6 +5154,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Via Ca Montanare 3</t>
@@ -4992,10 +5171,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>45.4721218</v>
+        <v>45.47412</v>
       </c>
       <c r="I86" t="n">
-        <v>11.4469703</v>
+        <v>11.43214</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5005,14 +5184,16 @@
       <c r="K86" t="n">
         <v>1</v>
       </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>45134</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5025,6 +5206,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Ceroni, 37</t>
@@ -5035,11 +5217,12 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>45.4083415</v>
+        <v>45.41214</v>
       </c>
       <c r="I87" t="n">
-        <v>11.5676593</v>
+        <v>11.54582</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5059,9 +5242,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>45137</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5074,6 +5258,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Via Ceroni, 37</t>
@@ -5084,11 +5269,12 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>45.4083415</v>
+        <v>45.41214</v>
       </c>
       <c r="I88" t="n">
-        <v>11.5676593</v>
+        <v>11.54582</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5108,9 +5294,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5123,6 +5310,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>viale Trenti 66</t>
@@ -5139,10 +5327,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>45.4437746</v>
+        <v>45.53985</v>
       </c>
       <c r="I89" t="n">
-        <v>11.6732113</v>
+        <v>11.52843</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -5152,14 +5340,16 @@
       <c r="K89" t="n">
         <v>1</v>
       </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5172,6 +5362,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Zemola 16</t>
@@ -5188,10 +5379,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>45.7852211</v>
+        <v>45.78652</v>
       </c>
       <c r="I90" t="n">
-        <v>11.426095</v>
+        <v>11.42815</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5211,9 +5402,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45144</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5226,6 +5418,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Barbarno Mossano</t>
@@ -5236,6 +5429,7 @@
           <t>Barbarno Mossano</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>45.4083415</v>
       </c>
@@ -5250,14 +5444,16 @@
       <c r="K91" t="n">
         <v>1</v>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5270,6 +5466,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Via Martin Luther King 39e</t>
@@ -5286,10 +5483,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>45.6413213</v>
+        <v>45.63581</v>
       </c>
       <c r="I92" t="n">
-        <v>11.3040596</v>
+        <v>11.3552</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5309,9 +5506,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5324,6 +5522,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -5353,14 +5552,16 @@
       <c r="K93" t="n">
         <v>1</v>
       </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45161</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5373,6 +5574,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Via Roma 8</t>
@@ -5389,10 +5591,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45.7338941</v>
+        <v>45.54472</v>
       </c>
       <c r="I94" t="n">
-        <v>11.3737893</v>
+        <v>11.54518</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5412,9 +5614,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45162</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -5427,6 +5630,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Via Giuseppe Zampieri 4</t>
@@ -5443,10 +5647,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>45.3650367</v>
+        <v>45.36214</v>
       </c>
       <c r="I95" t="n">
-        <v>11.4273627</v>
+        <v>11.42857</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5466,9 +5670,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45165</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -5481,6 +5686,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Via Cavour 77</t>
@@ -5497,10 +5703,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>45.4612318</v>
+        <v>45.47466</v>
       </c>
       <c r="I96" t="n">
-        <v>11.4235969</v>
+        <v>11.44421</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5520,9 +5726,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -5535,6 +5742,7 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Viale Riviera Berica 699</t>
@@ -5551,10 +5759,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>45.5038055</v>
+        <v>45.50341</v>
       </c>
       <c r="I97" t="n">
-        <v>11.5716547</v>
+        <v>11.58334</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5574,9 +5782,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -5589,6 +5798,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -5628,9 +5838,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>45174</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -5643,6 +5854,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Via Boito 19</t>
@@ -5659,10 +5871,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>45.5004723</v>
+        <v>45.50567</v>
       </c>
       <c r="I99" t="n">
-        <v>11.5356994</v>
+        <v>11.53812</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5682,9 +5894,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>45175</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -5697,6 +5910,7 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Torri di Arcugnano</t>
@@ -5736,9 +5950,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>45175</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -5751,6 +5966,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Stazione di Vicenza, 21</t>
@@ -5767,10 +5983,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>45.541644</v>
+        <v>45.53982</v>
       </c>
       <c r="I101" t="n">
-        <v>11.5407525</v>
+        <v>11.54015</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5790,9 +6006,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>45179</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -5805,6 +6022,7 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Asiago</t>
@@ -5844,9 +6062,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>45180</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -5859,6 +6078,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>via Pasquali Marana 33</t>
@@ -5875,10 +6095,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>45.6393262</v>
+        <v>45.54148</v>
       </c>
       <c r="I103" t="n">
-        <v>11.2105572</v>
+        <v>11.52843</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5898,9 +6118,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -5913,6 +6134,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Via Andrea Mantegna 7</t>
@@ -5929,10 +6151,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>45.5797865</v>
+        <v>45.54145</v>
       </c>
       <c r="I104" t="n">
-        <v>11.7388764</v>
+        <v>11.78589</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5952,9 +6174,10 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>45190</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -5967,6 +6190,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Cappuccini 65</t>
@@ -5983,10 +6207,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>45.6861778</v>
+        <v>45.69462</v>
       </c>
       <c r="I105" t="n">
-        <v>11.7041837</v>
+        <v>11.71698</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6006,9 +6230,10 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>45190</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6021,6 +6246,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -6060,9 +6286,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>45192</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6075,6 +6302,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Via Arturo Ferrarin 138</t>
@@ -6091,10 +6319,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>45.5196971</v>
+        <v>45.57018</v>
       </c>
       <c r="I107" t="n">
-        <v>11.3465936</v>
+        <v>11.53482</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -6114,9 +6342,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>45201</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6129,6 +6358,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6168,9 +6398,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>45225</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6183,6 +6414,7 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -6222,9 +6454,10 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6237,6 +6470,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Via Lago Maggiore 1</t>
@@ -6253,10 +6487,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>45.5004723</v>
+        <v>45.49841</v>
       </c>
       <c r="I110" t="n">
-        <v>11.5356994</v>
+        <v>11.53857</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6276,9 +6510,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>45276</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -6291,6 +6526,7 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Via Pietro Scalcerle, 5</t>
@@ -6307,10 +6543,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>45.5512985</v>
+        <v>45.55291</v>
       </c>
       <c r="I111" t="n">
-        <v>11.5272955</v>
+        <v>11.54523</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -6330,9 +6566,10 @@
           <t>in degenza</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45281</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -6345,6 +6582,7 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Contrà Barche, 40</t>
@@ -6361,10 +6599,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>45.5460888</v>
+        <v>45.54634</v>
       </c>
       <c r="I112" t="n">
-        <v>11.5501784</v>
+        <v>11.55135</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6384,6 +6622,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/src/main/assets/Pipistrelli 2023.xlsx
+++ b/app/src/main/assets/Pipistrelli 2023.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>45.60331</v>
+        <v>45.6499676</v>
       </c>
       <c r="I3" t="n">
-        <v>11.49392</v>
+        <v>11.4986907</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45.66547</v>
+        <v>45.6619177</v>
       </c>
       <c r="I5" t="n">
-        <v>11.37038</v>
+        <v>11.3639604</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.48512</v>
+        <v>45.4970909</v>
       </c>
       <c r="I6" t="n">
-        <v>11.48805</v>
+        <v>11.4894451</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>45.64205</v>
+        <v>45.645818</v>
       </c>
       <c r="I13" t="n">
-        <v>11.30653</v>
+        <v>11.2928279</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>45.53934</v>
+        <v>45.6348591</v>
       </c>
       <c r="I14" t="n">
-        <v>11.52309</v>
+        <v>11.4063543</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>45.63228</v>
+        <v>45.6403</v>
       </c>
       <c r="I16" t="n">
-        <v>11.55417</v>
+        <v>11.5512138</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.70132</v>
+        <v>45.6777651</v>
       </c>
       <c r="I17" t="n">
-        <v>11.64415</v>
+        <v>11.6434259</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.75391</v>
+        <v>45.7502752</v>
       </c>
       <c r="I18" t="n">
-        <v>11.72844</v>
+        <v>11.7221597</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45.75391</v>
+        <v>45.7502752</v>
       </c>
       <c r="I19" t="n">
-        <v>11.72844</v>
+        <v>11.7221597</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>45.5154</v>
+        <v>45.5140939</v>
       </c>
       <c r="I23" t="n">
-        <v>11.46247</v>
+        <v>11.4574964</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1743,7 +1743,11 @@
           <t>San Giorgio di Perlena</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>45.7304755</v>
       </c>
@@ -1797,10 +1801,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45.63551</v>
+        <v>45.6285174</v>
       </c>
       <c r="I25" t="n">
-        <v>11.54884</v>
+        <v>11.5476187</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1853,10 +1857,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>45.71346</v>
+        <v>45.7199703</v>
       </c>
       <c r="I26" t="n">
-        <v>11.35844</v>
+        <v>11.4133487</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1905,10 +1909,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>45.5342</v>
+        <v>45.53057</v>
       </c>
       <c r="I27" t="n">
-        <v>11.4845</v>
+        <v>11.4778668</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2013,10 +2017,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>45.55633</v>
+        <v>45.5560012</v>
       </c>
       <c r="I29" t="n">
-        <v>11.51875</v>
+        <v>11.519238</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2449,10 +2453,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>45.70679</v>
+        <v>45.7059893</v>
       </c>
       <c r="I37" t="n">
-        <v>11.47426</v>
+        <v>11.4797197</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2505,10 +2509,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>45.4542</v>
+        <v>45.4517637</v>
       </c>
       <c r="I38" t="n">
-        <v>11.3831</v>
+        <v>11.3824998</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2777,10 +2781,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>45.59552</v>
+        <v>45.5925277</v>
       </c>
       <c r="I43" t="n">
-        <v>11.58217</v>
+        <v>11.5686495</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2891,10 +2895,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>45.5312</v>
+        <v>45.529767</v>
       </c>
       <c r="I45" t="n">
-        <v>11.4883</v>
+        <v>11.455545</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2947,10 +2951,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45.70679</v>
+        <v>45.7059893</v>
       </c>
       <c r="I46" t="n">
-        <v>11.47426</v>
+        <v>11.4797197</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3032,8 +3036,10 @@
       <c r="A48" s="1" t="n">
         <v>45113</v>
       </c>
-      <c r="B48" s="1" t="n">
-        <v>22.525</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20:45:00</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3115,10 +3121,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>45.7081</v>
+        <v>45.7056839</v>
       </c>
       <c r="I49" t="n">
-        <v>11.5644</v>
+        <v>11.5678638</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3223,10 +3229,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>45.5401</v>
+        <v>45.5462004</v>
       </c>
       <c r="I51" t="n">
-        <v>11.5167</v>
+        <v>11.5104295</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3335,10 +3341,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45.55024</v>
+        <v>45.5501072</v>
       </c>
       <c r="I53" t="n">
-        <v>11.54345</v>
+        <v>11.5457041</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3449,10 +3455,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>45.54928</v>
+        <v>45.5496207</v>
       </c>
       <c r="I55" t="n">
-        <v>11.55404</v>
+        <v>11.5536058</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3501,10 +3507,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>45.49845</v>
+        <v>45.5050793</v>
       </c>
       <c r="I56" t="n">
-        <v>11.41725</v>
+        <v>11.4084448</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3609,10 +3615,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>45.53982</v>
+        <v>45.6348591</v>
       </c>
       <c r="I58" t="n">
-        <v>11.53112</v>
+        <v>11.4063543</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3723,10 +3729,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>45.55225</v>
+        <v>45.5526214</v>
       </c>
       <c r="I60" t="n">
-        <v>11.54316</v>
+        <v>11.5426385</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3779,10 +3785,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>45.62635</v>
+        <v>45.5479</v>
       </c>
       <c r="I61" t="n">
-        <v>11.54228</v>
+        <v>11.5446</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3837,10 +3843,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>45.6329</v>
+        <v>45.6355174</v>
       </c>
       <c r="I62" t="n">
-        <v>11.54884</v>
+        <v>11.5485978</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4005,10 +4011,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>45.34415</v>
+        <v>45.3362423</v>
       </c>
       <c r="I65" t="n">
-        <v>11.53912</v>
+        <v>11.5394891</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4117,10 +4123,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>45.53238</v>
+        <v>45.7116058</v>
       </c>
       <c r="I67" t="n">
-        <v>11.51655</v>
+        <v>11.4928835</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45.71968</v>
+        <v>45.6987902</v>
       </c>
       <c r="I69" t="n">
-        <v>11.36384</v>
+        <v>11.3981595</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4285,10 +4291,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>45.54751</v>
+        <v>45.5470273</v>
       </c>
       <c r="I70" t="n">
-        <v>11.54583</v>
+        <v>11.5434297</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4399,10 +4405,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>45.54582</v>
+        <v>45.6988924</v>
       </c>
       <c r="I72" t="n">
-        <v>11.51654</v>
+        <v>11.5573731</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4791,10 +4797,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>45.71714</v>
+        <v>45.7113511</v>
       </c>
       <c r="I79" t="n">
-        <v>11.36531</v>
+        <v>11.3553593</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4847,10 +4853,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>45.66014</v>
+        <v>45.6585696</v>
       </c>
       <c r="I80" t="n">
-        <v>11.41721</v>
+        <v>11.405103</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4903,10 +4909,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>45.71215</v>
+        <v>45.7051709</v>
       </c>
       <c r="I81" t="n">
-        <v>11.23412</v>
+        <v>11.2249347</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5113,12 +5119,16 @@
           <t>Zané</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H85" t="n">
-        <v>45.72314</v>
+        <v>45.7201187</v>
       </c>
       <c r="I85" t="n">
-        <v>11.44853</v>
+        <v>11.4608274</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5171,10 +5181,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>45.47412</v>
+        <v>45.4721218</v>
       </c>
       <c r="I86" t="n">
-        <v>11.43214</v>
+        <v>11.4469703</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5214,15 +5224,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barbarno Mossano</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Barbarano Mossano</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H87" t="n">
-        <v>45.41214</v>
+        <v>45.4101</v>
       </c>
       <c r="I87" t="n">
-        <v>11.54582</v>
+        <v>11.5422</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5266,15 +5280,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barbarno Mossano</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Barbarano Mossano</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H88" t="n">
-        <v>45.41214</v>
+        <v>45.4101</v>
       </c>
       <c r="I88" t="n">
-        <v>11.54582</v>
+        <v>11.5422</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5327,10 +5345,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>45.53985</v>
+        <v>45.4437746</v>
       </c>
       <c r="I89" t="n">
-        <v>11.52843</v>
+        <v>11.6732113</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -5354,12 +5372,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>13:42:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Miniopterus schreibersii</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -5370,7 +5388,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cogollo Del Cengio</t>
+          <t>Barbarano Vicentino</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5379,14 +5397,14 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>45.78652</v>
+        <v>45.4101</v>
       </c>
       <c r="I90" t="n">
-        <v>11.42815</v>
+        <v>11.5422</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>subadulto</t>
+          <t>adulto</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -5394,23 +5412,23 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>non vola</t>
+          <t>Trauma da impatto lieve</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>morto</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45144</v>
+        <v>45142</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20:32:00</t>
+          <t>14:36:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5421,20 +5439,24 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Barbarno Mossano</t>
+          <t>Via Giovanni ventriseesimo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barbarno Mossano</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>Cogollo Del Cengio</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H91" t="n">
-        <v>45.4083415</v>
+        <v>45.7852211</v>
       </c>
       <c r="I91" t="n">
-        <v>11.5676593</v>
+        <v>11.426095</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5444,7 +5466,11 @@
       <c r="K91" t="n">
         <v>1</v>
       </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>non vola</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>morto</t>
@@ -5454,11 +5480,11 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45155</v>
+        <v>45144</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>09:33:00</t>
+          <t>20:32:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5469,12 +5495,12 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Via Martin Luther King 39e</t>
+          <t>Barbarno Mossano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Valdagno</t>
+          <t>Barbarano Mossano</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5483,10 +5509,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>45.63581</v>
+        <v>45.4101</v>
       </c>
       <c r="I92" t="n">
-        <v>11.3552</v>
+        <v>11.5422</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5496,14 +5522,10 @@
       <c r="K92" t="n">
         <v>1</v>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>cucciolo aggrappato ad un palo</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>liberato</t>
+          <t>morto</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -5514,7 +5536,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>09:33:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5525,12 +5547,12 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rosà</t>
+          <t>Via Martin Luther King 39e</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosà</t>
+          <t>Valdagno</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5539,10 +5561,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>45.7244163</v>
+        <v>45.6413213</v>
       </c>
       <c r="I93" t="n">
-        <v>11.7626859</v>
+        <v>11.3040596</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5552,37 +5574,41 @@
       <c r="K93" t="n">
         <v>1</v>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>cucciolo aggrappato ad un palo</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>morto</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45161</v>
+        <v>45155</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:25:00</t>
+          <t>11:25:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hypsugo savii</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Via Roma 8</t>
+          <t>Rosà</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Rosà</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5591,24 +5617,20 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45.54472</v>
+        <v>45.7244163</v>
       </c>
       <c r="I94" t="n">
-        <v>11.54518</v>
+        <v>11.7626859</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>adulto</t>
+          <t>subadulto</t>
         </is>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Predato dal gatto con tanto sangue</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>morto</t>
@@ -5618,11 +5640,11 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45162</v>
+        <v>45161</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>16:25:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5633,12 +5655,12 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Via Giuseppe Zampieri 4</t>
+          <t>Via Roma 8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alonte</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5647,10 +5669,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>45.36214</v>
+        <v>45.7338941</v>
       </c>
       <c r="I95" t="n">
-        <v>11.42857</v>
+        <v>11.3737893</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5662,7 +5684,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Pieno di zecche</t>
+          <t>Predato dal gatto con tanto sangue</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5674,11 +5696,11 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45165</v>
+        <v>45162</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:08:00</t>
+          <t>10:27:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5689,12 +5711,12 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Via Cavour 77</t>
+          <t>Via Giuseppe Zampieri 4</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brendola</t>
+          <t>Alonte</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5703,14 +5725,14 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>45.47466</v>
+        <v>45.3650367</v>
       </c>
       <c r="I96" t="n">
-        <v>11.44421</v>
+        <v>11.4273627</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>subadulto</t>
+          <t>adulto</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -5718,7 +5740,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>magrissimo</t>
+          <t>Pieno di zecche</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5730,27 +5752,27 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45169</v>
+        <v>45165</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18:16:00</t>
+          <t>16:08:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Hypsugo savii</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Viale Riviera Berica 699</t>
+          <t>Via Cavour 77</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Brendola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5759,14 +5781,14 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>45.50341</v>
+        <v>45.4612318</v>
       </c>
       <c r="I97" t="n">
-        <v>11.58334</v>
+        <v>11.4235969</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>adulto</t>
+          <t>subadulto</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -5774,51 +5796,51 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>All'interno del cassettone, della taparella di casa.</t>
+          <t>magrissimo</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>liberato</t>
+          <t>morto</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45170</v>
+        <v>45169</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:53:00</t>
+          <t>18:16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hypsugo savii</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Viale Riviera Berica 699</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>Vicenza</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Vicenza</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>45.6348591</v>
+        <v>45.5038055</v>
       </c>
       <c r="I98" t="n">
-        <v>11.4063543</v>
+        <v>11.5716547</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5830,7 +5852,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>trovato a terra debilitato</t>
+          <t>All'interno del cassettone, della taparella di casa.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5842,27 +5864,27 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45174</v>
+        <v>45170</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>09:20:00</t>
+          <t>15:53:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Hypsugo savii</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Via Boito 19</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Arcugnano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5871,14 +5893,14 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>45.50567</v>
+        <v>45.6348591</v>
       </c>
       <c r="I99" t="n">
-        <v>11.53812</v>
+        <v>11.4063543</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>subadulto</t>
+          <t>adulto</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -5886,34 +5908,34 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>trovato in terra, frattura omero</t>
+          <t>trovato a terra debilitato</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>morto</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45175</v>
+        <v>45174</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:02:00</t>
+          <t>09:20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torri di Arcugnano</t>
+          <t>Via Boito 19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5927,14 +5949,14 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>45.4930641</v>
+        <v>45.5004723</v>
       </c>
       <c r="I100" t="n">
-        <v>11.5481101</v>
+        <v>11.5356994</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>adulto</t>
+          <t>subadulto</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -5942,12 +5964,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>dentro l'aspiratore del bagno</t>
+          <t>trovato in terra, frattura omero</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>liberato</t>
+          <t>morto</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -5958,23 +5980,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>19:04:00</t>
+          <t>17:02:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stazione di Vicenza, 21</t>
+          <t>Torri di Arcugnano</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Arcugnano</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5983,10 +6005,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>45.53982</v>
+        <v>45.4930641</v>
       </c>
       <c r="I101" t="n">
-        <v>11.54015</v>
+        <v>11.5481101</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5998,39 +6020,39 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Frattura</t>
+          <t>dentro l'aspiratore del bagno</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>morto</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45179</v>
+        <v>45175</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>19:04:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Asiago</t>
+          <t>Stazione di Vicenza, 21</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Asiago</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6039,10 +6061,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>45.8753771</v>
+        <v>45.541644</v>
       </c>
       <c r="I102" t="n">
-        <v>11.5106998</v>
+        <v>11.5407525</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -6054,39 +6076,39 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>debilitato</t>
+          <t>Frattura</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>liberato</t>
+          <t>morto</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45180</v>
+        <v>45179</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:21:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>via Pasquali Marana 33</t>
+          <t>Asiago</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Asiago</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6095,10 +6117,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>45.54148</v>
+        <v>45.8753771</v>
       </c>
       <c r="I103" t="n">
-        <v>11.52843</v>
+        <v>11.5106998</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6110,7 +6132,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>All'interno della tabaccheria della stazione su una luce</t>
+          <t>debilitato</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6122,11 +6144,11 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45184</v>
+        <v>45180</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>06:54:00</t>
+          <t>20:21:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6137,24 +6159,24 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Via Andrea Mantegna 7</t>
+          <t>via Pasquali Marana 33</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Piazzola Sul Brenta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>VI</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>45.54145</v>
+        <v>45.6393262</v>
       </c>
       <c r="I104" t="n">
-        <v>11.78589</v>
+        <v>11.2105572</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6166,23 +6188,23 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>frattura del radio, messo chiodino</t>
+          <t>All'interno della tabaccheria della stazione su una luce</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>in degenza</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45190</v>
+        <v>45184</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>10:06:00</t>
+          <t>06:54:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6193,28 +6215,28 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Via Cappuccini 65</t>
+          <t>Via Andrea Mantegna 7</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tezze Sul Brenta</t>
+          <t>Piazzola Sul Brenta</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>45.69462</v>
+        <v>45.5797865</v>
       </c>
       <c r="I105" t="n">
-        <v>11.71698</v>
+        <v>11.7388764</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>subadulto</t>
+          <t>adulto</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -6222,7 +6244,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>ferito, patagio strappato</t>
+          <t>frattura del radio, messo chiodino</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -6238,7 +6260,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:02:00</t>
+          <t>10:06:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6249,12 +6271,12 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Creazzo</t>
+          <t>Via Cappuccini 65</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Creazzo</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6263,10 +6285,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>45.5320528</v>
+        <v>45.6861778</v>
       </c>
       <c r="I106" t="n">
-        <v>11.4785807</v>
+        <v>11.7041837</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -6278,39 +6300,39 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>All'interno dell'istituto  2 Giugno</t>
+          <t>ferito, patagio strappato</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>liberato</t>
+          <t>in degenza</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45192</v>
+        <v>45190</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>11:06:00</t>
+          <t>20:02:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hypsugo savii</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Via Arturo Ferrarin 138</t>
+          <t>Creazzo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Creazzo</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6319,10 +6341,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>45.57018</v>
+        <v>45.5320528</v>
       </c>
       <c r="I107" t="n">
-        <v>11.53482</v>
+        <v>11.4785807</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -6334,7 +6356,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>debilitato</t>
+          <t>All'interno dell'istituto  2 Giugno</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6346,39 +6368,39 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45201</v>
+        <v>45192</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:08:00</t>
+          <t>11:06:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Hypsugo savii</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
+          <t>Via Arturo Ferrarin 138</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>Vicenza</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Vicenza</t>
-        </is>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>45.6348591</v>
+        <v>45.5196971</v>
       </c>
       <c r="I108" t="n">
-        <v>11.4063543</v>
+        <v>11.3465936</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -6390,7 +6412,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>trovato dentro la caserma</t>
+          <t>debilitato</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6402,27 +6424,27 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45225</v>
+        <v>45201</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>08:43:00</t>
+          <t>18:08:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Schio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Schio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6431,10 +6453,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>45.7113511</v>
+        <v>45.6348591</v>
       </c>
       <c r="I109" t="n">
-        <v>11.3553593</v>
+        <v>11.4063543</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -6446,39 +6468,39 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>trovato in fabbrica, molto debilitato</t>
+          <t>trovato dentro la caserma</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>in degenza</t>
+          <t>liberato</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45245</v>
+        <v>45225</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>10:04:00</t>
+          <t>08:43:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pipistrellus sp.</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Via Lago Maggiore 1</t>
+          <t>Schio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Arcugnano</t>
+          <t>Schio</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6487,10 +6509,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>45.49841</v>
+        <v>45.7113511</v>
       </c>
       <c r="I110" t="n">
-        <v>11.53857</v>
+        <v>11.3553593</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6502,39 +6524,39 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>predato da gatto</t>
+          <t>trovato in fabbrica, molto debilitato</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>morto</t>
+          <t>in degenza</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45276</v>
+        <v>45245</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>10:04:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hypsugo savii</t>
+          <t>Pipistrellus sp.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Via Pietro Scalcerle, 5</t>
+          <t>Via Lago Maggiore 1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Arcugnano</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6543,14 +6565,14 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>45.55291</v>
+        <v>45.5004723</v>
       </c>
       <c r="I111" t="n">
-        <v>11.54523</v>
+        <v>11.5356994</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>adulto</t>
+          <t>subadulto</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -6558,71 +6580,127 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>caduto mentre avvolgeva la serranda della finestra</t>
+          <t>predato da gatto</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>in degenza</t>
+          <t>morto</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45281</v>
+        <v>45276</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>11:28:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pipistrellus kuhlii</t>
+          <t>Hypsugo savii</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
+          <t>Via Pietro Scalcerle, 5</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vicenza</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>45.5512985</v>
+      </c>
+      <c r="I112" t="n">
+        <v>11.5272955</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>adulto</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>caduto mentre avvolgeva la serranda della finestra</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>in degenza</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pipistrellus kuhlii</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Contrà Barche, 40</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Vicenza</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
-        <v>45.54634</v>
-      </c>
-      <c r="I112" t="n">
-        <v>11.55135</v>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>45.5460888</v>
+      </c>
+      <c r="I113" t="n">
+        <v>11.5501784</v>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>adulto</t>
         </is>
       </c>
-      <c r="K112" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" t="inlineStr">
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>caduto mentre chiudeva le persiane, arrivato morto</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>morto</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
